--- a/EXCEL/Data/særydelser-og-merarbejde/merarbejde_regioner.xlsx
+++ b/EXCEL/Data/særydelser-og-merarbejde/merarbejde_regioner.xlsx
@@ -85,7 +85,7 @@
     <t>Datasæt 02 2014</t>
   </si>
   <si>
-    <t>Kørsel 10.4.2026 11.28.47</t>
+    <t>Kørsel 14.4.2026 12.27.08</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
